--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.35.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.35.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0035.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0035.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -596,21 +596,25 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A Ã€</t>
+          <t>L44: suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A À</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ ena to rejoin is not now necessary, but the cause</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+91D1 CJK UNIFIED IDEOGRAPH-91D1 | isolated marker/symbol line :: 金</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A Ã€</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L14: isolated marker/symbol line :: 28</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: I-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -628,7 +632,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • We command you, that within days after the</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,26 +666,22 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: As respects such Defendant, the writ is as follows :â€” %</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • We command you, that within days after the</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: é‡‘</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+91D1 CJK UNIFIED IDEOGRAPH-91D1 | isolated marker/symbol line :: 金</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: , /</t>
+          <t>L30: isolated marker/symbol line :: I-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -713,16 +717,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subpo Ã¦ ena to</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ We command you, that within days after the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -732,7 +728,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 1</t>
+          <t>L32: isolated marker/symbol line :: , /</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -769,21 +765,17 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Plaintiffâ€™s Solicitor.</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L28: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1850.</t>
+          <t>L34: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -820,11 +812,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: liberty to file his rÃ©plication.!</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -834,7 +822,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 1%</t>
+          <t>L59: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -881,7 +869,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: -A</t>
+          <t>L65: isolated marker/symbol line :: 1%</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -924,7 +912,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: I</t>
+          <t>L69: isolated marker/symbol line :: -A</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -965,7 +953,11 @@
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -985,12 +977,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1029,7 +1021,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1068,7 +1060,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1146,7 +1138,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
